--- a/配置表格/__tables__.xlsx
+++ b/配置表格/__tables__.xlsx
@@ -697,14 +697,10 @@
           <x:t xml:space="preserve">config_id</x:t>
         </x:is>
       </x:c>
-      <x:c r="H8" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">s</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H8" s="1"/>
       <x:c r="I8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">怪物刷新配置</x:t>
+          <x:t xml:space="preserve">怪物刷新配置（客户端只导 config_id + activity：刷怪方案刷出的怪跑什么日常；方案内容仍只给服务端）</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="4" t="inlineStr">
@@ -1258,7 +1254,7 @@
       </x:c>
       <x:c r="E23" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sound_config@Z音频配置表.xlsx</x:t>
+          <x:t xml:space="preserve">sound_config@Y音频配置表.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="4" t="inlineStr">
@@ -1368,7 +1364,7 @@
       </x:c>
       <x:c r="E25" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon_config@Z图标配置表.xlsx</x:t>
+          <x:t xml:space="preserve">icon_config@T图标配置表.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="4" t="inlineStr">
@@ -2571,7 +2567,7 @@
       </x:c>
       <x:c r="F51" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigID</x:t>
+          <x:t xml:space="preserve">config_id</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="4" t="n"/>
@@ -2607,8 +2603,10 @@
         <x:v>map</x:v>
       </x:c>
       <x:c r="H52"/>
-      <x:c r="I52" t="str">
-        <x:v>神通词条配置</x:v>
+      <x:c r="I52" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">词条配置：一行一条词条，作用对象 + 修改1～修改4（每块一次修改）</x:t>
+        </x:is>
       </x:c>
       <x:c r="J52"/>
       <x:c r="K52" t="str">
@@ -2644,6 +2642,261 @@
         <x:v>skill_zhenyi_config</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="B54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbOwnedEntityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OwnedEntityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">owned_entity_config@Z从属实体表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从属实体表（召唤兽/图腾/地板/火蛇；有主人、有生命周期的场上实体，将来契约宠物也在此）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">owned_entity_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="B55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbAiProfileConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AiProfileConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ai_profile@G怪物NPC行为表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">怪物 AI 参数组（搜索间隔 / 脱战 / 回防；monster_config.ai_profile、owned_entity_config.ai_profile、npc_config.ai_profile 引用，全体法宝共用的一行由法宝全局参数 BehaviorProfile 引用）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ai_profile</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="B56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbActivityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">activity_config@G怪物NPC行为表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日常活动模板（驻留 / 巡逻 / 游走 / 跟随 / 漂移 / 绕飞；spawn_config.activity、npc_config.activity、owned_entity_config.activity 引用，全体法宝共用的一行由法宝全局参数 DailyActivity 引用）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">activity_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="B57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbQuestConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_config@R任务表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务表：一行一个任务；无标列两端都读，c 列只给客户端</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="B58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbQuestStepConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestStepConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_step_config@R任务表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_id+step_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">list</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务步骤表：一行一个步骤，主键 quest_id+step_id；顺序由 next_step 决定，不是 step_id 大小</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_step_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="B59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbCurrencyConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CurrencyConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConfigAssets@X系统参数.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">货币配置：一行一种货币（名称、图标、说明、是否账号共享）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">currency_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/配置表格/__tables__.xlsx
+++ b/配置表格/__tables__.xlsx
@@ -833,7 +833,7 @@
       </x:c>
       <x:c r="E12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">equip_config@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">装备@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigQianghua@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">强化@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </x:c>
       <x:c r="E14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigXiaojiping@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">灵蕴@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </x:c>
       <x:c r="E15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigLianhua@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">炼化@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">hidden_attribute</x:t>
+          <x:t xml:space="preserve">hidden_affix</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" s="4" t="n"/>
@@ -981,7 +981,7 @@
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigCitiao@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">道纹@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ConfigTaozhuang@Z装备.xlsx</x:t>
+          <x:t xml:space="preserve">套装@Z装备.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="2" t="inlineStr">
@@ -2164,46 +2164,16 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="4" t="str"/>
-      <x:c r="B42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbFabaoRefineConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FabaoRefineConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">祭炼@F法宝.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refine_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B42" s="4"/>
+      <x:c r="C42" s="4"/>
+      <x:c r="D42" s="4"/>
+      <x:c r="E42" s="4"/>
+      <x:c r="F42" s="4"/>
+      <x:c r="G42" s="4"/>
       <x:c r="H42" s="4" t="str"/>
-      <x:c r="I42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">法宝祭炼层配置</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="I42" s="4"/>
       <x:c r="J42" s="4" t="str"/>
-      <x:c r="K42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fabao_refine_config</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="K42" s="4"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="4" t="str"/>

--- a/配置表格/__tables__.xlsx
+++ b/配置表格/__tables__.xlsx
@@ -950,7 +950,7 @@
       </x:c>
       <x:c r="F15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">hidden_affix</x:t>
+          <x:t xml:space="preserve">refine_id</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" s="4" t="n"/>
@@ -2867,6 +2867,46 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="60">
+      <x:c r="B60" s="2" t="inlineStr">
+        <x:is>
+          <x:t>TbCosmeticConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="2" t="inlineStr">
+        <x:is>
+          <x:t>CosmeticConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E60" s="2" t="inlineStr">
+        <x:is>
+          <x:t>cosmetic_config@H幻化配置表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="2" t="inlineStr">
+        <x:is>
+          <x:t>id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" t="inlineStr">
+        <x:is>
+          <x:t>map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I60" s="2" t="inlineStr">
+        <x:is>
+          <x:t>幻化配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K60" s="4" t="inlineStr">
+        <x:is>
+          <x:t>cosmetic_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/配置表格/__tables__.xlsx
+++ b/配置表格/__tables__.xlsx
@@ -1728,17 +1728,15 @@
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A33" s="4" t="str"/>
       <x:c r="B33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyQualityConfig</x:t>
+          <x:t xml:space="preserve">TbFabaoConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyQualityConfig</x:t>
+          <x:t xml:space="preserve">FabaoConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="4" t="b">
@@ -1746,12 +1744,12 @@
       </x:c>
       <x:c r="E33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyQuality@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">法宝@F法宝.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">fabao_id</x:t>
         </x:is>
       </x:c>
       <x:c r="G33" s="4" t="inlineStr">
@@ -1759,133 +1757,85 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H33" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H33" s="4" t="str"/>
       <x:c r="I33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹品质参数</x:t>
+          <x:t xml:space="preserve">法宝主配置</x:t>
         </x:is>
       </x:c>
       <x:c r="J33" s="4" t="str"/>
       <x:c r="K33" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_quality_config</x:t>
+          <x:t xml:space="preserve">fabao_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbAlchemyRealmConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AlchemyRealmConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AlchemyRealm@X系统参数.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G34" s="4" t="inlineStr">
+      <x:c r="A34" s="4" t="str"/>
+      <x:c r="B34" s="4"/>
+      <x:c r="C34" s="4"/>
+      <x:c r="D34" s="4"/>
+      <x:c r="E34" s="4"/>
+      <x:c r="F34" s="4"/>
+      <x:c r="G34" s="4"/>
+      <x:c r="H34" s="4" t="str"/>
+      <x:c r="I34" s="4"/>
+      <x:c r="J34" s="4" t="str"/>
+      <x:c r="K34" s="4"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="4" t="str"/>
+      <x:c r="B35" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbFabaoForgeConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FabaoForgeConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">打造@F法宝.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">fabao_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">炼丹境界差参数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J34" s="4" t="str"/>
-      <x:c r="K34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">alchemy_realm_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbAlchemyFurnaceParamConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AlchemyFurnaceParamConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AlchemyFurnace@X系统参数.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H35" s="4" t="str"/>
       <x:c r="I35" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹丹炉品质参数</x:t>
+          <x:t xml:space="preserve">法宝打造配方</x:t>
         </x:is>
       </x:c>
       <x:c r="J35" s="4" t="str"/>
       <x:c r="K35" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_furnace_param_config</x:t>
+          <x:t xml:space="preserve">fabao_forge_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A36" s="4" t="str"/>
       <x:c r="B36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyPressureConfig</x:t>
+          <x:t xml:space="preserve">TbFabaoPowerWeightConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyPressureConfig</x:t>
+          <x:t xml:space="preserve">FabaoPowerWeightConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D36" s="4" t="b">
@@ -1893,12 +1843,12 @@
       </x:c>
       <x:c r="E36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyPressure@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">威能权重@F法宝.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">attr_key</x:t>
         </x:is>
       </x:c>
       <x:c r="G36" s="4" t="inlineStr">
@@ -1906,35 +1856,29 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H36" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H36" s="4" t="str"/>
       <x:c r="I36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹炉压参数</x:t>
+          <x:t xml:space="preserve">法宝威能展示权重</x:t>
         </x:is>
       </x:c>
       <x:c r="J36" s="4" t="str"/>
       <x:c r="K36" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_pressure_config</x:t>
+          <x:t xml:space="preserve">fabao_power_weight_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A37" s="4" t="str"/>
       <x:c r="B37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyRemoveConfig</x:t>
+          <x:t xml:space="preserve">TbFabaoGlobalConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyRemoveConfig</x:t>
+          <x:t xml:space="preserve">FabaoGlobalConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" s="4" t="b">
@@ -1942,12 +1886,12 @@
       </x:c>
       <x:c r="E37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyRemove@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">全局参数@F法宝.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">param_key</x:t>
         </x:is>
       </x:c>
       <x:c r="G37" s="4" t="inlineStr">
@@ -1955,35 +1899,29 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H37" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H37" s="4" t="str"/>
       <x:c r="I37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹剔杂参数</x:t>
+          <x:t xml:space="preserve">法宝全局参数</x:t>
         </x:is>
       </x:c>
       <x:c r="J37" s="4" t="str"/>
       <x:c r="K37" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_remove_config</x:t>
+          <x:t xml:space="preserve">fabao_global_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A38" s="4" t="str"/>
       <x:c r="B38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyPoisonConfig</x:t>
+          <x:t xml:space="preserve">TbQizhenConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyPoisonConfig</x:t>
+          <x:t xml:space="preserve">QizhenConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="4" t="b">
@@ -1991,12 +1929,12 @@
       </x:c>
       <x:c r="E38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyPoison@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">收录@Q奇珍录.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">qz_id</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="4" t="inlineStr">
@@ -2004,35 +1942,29 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H38" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H38" s="4" t="str"/>
       <x:c r="I38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹丹毒参数</x:t>
+          <x:t xml:space="preserve">奇珍收录主配置</x:t>
         </x:is>
       </x:c>
       <x:c r="J38" s="4" t="str"/>
       <x:c r="K38" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_poison_config</x:t>
+          <x:t xml:space="preserve">qizhen_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A39" s="4" t="str"/>
       <x:c r="B39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyLuckConfig</x:t>
+          <x:t xml:space="preserve">TbQizhenCodexConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyLuckConfig</x:t>
+          <x:t xml:space="preserve">QizhenCodexConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="4" t="b">
@@ -2040,12 +1972,12 @@
       </x:c>
       <x:c r="E39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyLuck@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">奇缘图谱@Q奇珍录.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">codex_id</x:t>
         </x:is>
       </x:c>
       <x:c r="G39" s="4" t="inlineStr">
@@ -2053,35 +1985,29 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H39" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H39" s="4" t="str"/>
       <x:c r="I39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹正向惊喜参数</x:t>
+          <x:t xml:space="preserve">奇缘图谱配置</x:t>
         </x:is>
       </x:c>
       <x:c r="J39" s="4" t="str"/>
       <x:c r="K39" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_luck_config</x:t>
+          <x:t xml:space="preserve">qizhen_codex_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
+      <x:c r="A40" s="4" t="str"/>
       <x:c r="B40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbAlchemyRateTextConfig</x:t>
+          <x:t xml:space="preserve">TbQizhenCarryConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyRateTextConfig</x:t>
+          <x:t xml:space="preserve">QizhenCarryConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="4" t="b">
@@ -2089,12 +2015,12 @@
       </x:c>
       <x:c r="E40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AlchemyRateText@X系统参数.xlsx</x:t>
+          <x:t xml:space="preserve">可携带@Q奇珍录.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">id</x:t>
+          <x:t xml:space="preserve">qz_id</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="4" t="inlineStr">
@@ -2102,20 +2028,16 @@
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H40" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="H40" s="4" t="str"/>
       <x:c r="I40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">炼丹成丹率提示参数</x:t>
+          <x:t xml:space="preserve">可携带奇珍配置</x:t>
         </x:is>
       </x:c>
       <x:c r="J40" s="4" t="str"/>
       <x:c r="K40" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">alchemy_rate_text_config</x:t>
+          <x:t xml:space="preserve">qizhen_carry_config</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2123,12 +2045,12 @@
       <x:c r="A41" s="4" t="str"/>
       <x:c r="B41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbFabaoConfig</x:t>
+          <x:t xml:space="preserve">TbQizhenCarrySlotConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FabaoConfig</x:t>
+          <x:t xml:space="preserve">QizhenCarrySlotConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="4" t="b">
@@ -2136,12 +2058,12 @@
       </x:c>
       <x:c r="E41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">法宝@F法宝.xlsx</x:t>
+          <x:t xml:space="preserve">携带位@Q奇珍录.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">fabao_id</x:t>
+          <x:t xml:space="preserve">carry_part</x:t>
         </x:is>
       </x:c>
       <x:c r="G41" s="4" t="inlineStr">
@@ -2152,39 +2074,65 @@
       <x:c r="H41" s="4" t="str"/>
       <x:c r="I41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">法宝主配置</x:t>
+          <x:t xml:space="preserve">奇珍携带位配置</x:t>
         </x:is>
       </x:c>
       <x:c r="J41" s="4" t="str"/>
       <x:c r="K41" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">fabao_config</x:t>
+          <x:t xml:space="preserve">qizhen_carry_slot_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="4" t="str"/>
-      <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4"/>
-      <x:c r="D42" s="4"/>
-      <x:c r="E42" s="4"/>
-      <x:c r="F42" s="4"/>
-      <x:c r="G42" s="4"/>
-      <x:c r="H42" s="4" t="str"/>
-      <x:c r="I42" s="4"/>
-      <x:c r="J42" s="4" t="str"/>
-      <x:c r="K42" s="4"/>
+      <x:c r="B42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbNpcConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NpcConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">npc_config@NPC配置表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NPC配置表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K42" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">npc_config</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="4" t="str"/>
       <x:c r="B43" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">TbFabaoForgeConfig</x:t>
+          <x:t xml:space="preserve">TbSystemVarConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">FabaoForgeConfig</x:t>
+          <x:t xml:space="preserve">SystemVarConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="4" t="b">
@@ -2192,448 +2140,451 @@
       </x:c>
       <x:c r="E43" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">打造@F法宝.xlsx</x:t>
+          <x:t xml:space="preserve">ConfigSystemVar@X系统参数.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">fabao_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G43" s="4" t="inlineStr">
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" s="4" t="n"/>
+      <x:c r="I43" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">系统参数（含炼丹四参数）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K43" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">system_var_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44"/>
+      <x:c r="B44" t="str">
+        <x:v>TbAffixConfig</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>AffixConfig</x:v>
+      </x:c>
+      <x:c r="D44" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>affix_config@C词条表.xlsx</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H44"/>
+      <x:c r="I44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">词条配置：一行一条词条，作用对象 + 修改1～修改4（每块一次修改）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J44"/>
+      <x:c r="K44" t="str">
+        <x:v>affix_config</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45" t="str">
+        <x:v>TbSkillZhenyiConfig</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>SkillZhenyiConfig</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>神通真意@S神通真意表.xlsx</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H45"/>
+      <x:c r="I45" t="str">
+        <x:v>神通真意配置</x:v>
+      </x:c>
+      <x:c r="J45"/>
+      <x:c r="K45" t="str">
+        <x:v>skill_zhenyi_config</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="B46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbOwnedEntityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OwnedEntityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">owned_entity_config@Z从属实体表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H43" s="4" t="str"/>
-      <x:c r="I43" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">法宝打造配方</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J43" s="4" t="str"/>
-      <x:c r="K43" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fabao_forge_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="4" t="str"/>
-      <x:c r="B44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbFabaoPowerWeightConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FabaoPowerWeightConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">威能权重@F法宝.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">attr_key</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G44" s="4" t="inlineStr">
+      <x:c r="H46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从属实体表（召唤兽/图腾/地板/火蛇；有主人、有生命周期的场上实体，将来契约宠物也在此）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">owned_entity_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="B47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbAiProfileConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AiProfileConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ai_profile@G怪物NPC行为表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H44" s="4" t="str"/>
-      <x:c r="I44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">法宝威能展示权重</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J44" s="4" t="str"/>
-      <x:c r="K44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fabao_power_weight_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="4" t="str"/>
-      <x:c r="B45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbFabaoGlobalConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FabaoGlobalConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D45" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">全局参数@F法宝.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">param_key</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G45" s="4" t="inlineStr">
+      <x:c r="H47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">怪物 AI 参数组（搜索间隔 / 脱战 / 回防；monster_config.ai_profile、owned_entity_config.ai_profile、npc_config.ai_profile 引用，全体法宝共用的一行由法宝全局参数 BehaviorProfile 引用）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ai_profile</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="B48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbActivityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ActivityConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">activity_config@G怪物NPC行为表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H45" s="4" t="str"/>
-      <x:c r="I45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">法宝全局参数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J45" s="4" t="str"/>
-      <x:c r="K45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fabao_global_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="4" t="str"/>
-      <x:c r="B46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQizhenConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QizhenConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D46" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">收录@Q奇珍录.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qz_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="4" t="inlineStr">
+      <x:c r="H48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日常活动模板（驻留 / 巡逻 / 游走 / 跟随 / 漂移 / 绕飞；spawn_config.activity、npc_config.activity、owned_entity_config.activity 引用，全体法宝共用的一行由法宝全局参数 DailyActivity 引用）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">activity_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="B49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbQuestConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_config@R任务表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H46" s="4" t="str"/>
-      <x:c r="I46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奇珍收录主配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J46" s="4" t="str"/>
-      <x:c r="K46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qizhen_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="4" t="str"/>
-      <x:c r="B47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQizhenCodexConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QizhenCodexConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D47" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奇缘图谱@Q奇珍录.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">codex_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G47" s="4" t="inlineStr">
+      <x:c r="I49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务表：一行一个任务；无标列两端都读，c 列只给客户端</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="B50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbQuestStepConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QuestStepConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_step_config@R任务表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_id+step_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">list</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任务步骤表：一行一个步骤，主键 quest_id+step_id；顺序由 next_step 决定，不是 step_id 大小</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quest_step_config</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="B51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbCurrencyConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CurrencyConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConfigAssets@X系统参数.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">config_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
-      <x:c r="H47" s="4" t="str"/>
-      <x:c r="I47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奇缘图谱配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J47" s="4" t="str"/>
-      <x:c r="K47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qizhen_codex_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="4" t="str"/>
-      <x:c r="B48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQizhenCarryConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QizhenCarryConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D48" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">可携带@Q奇珍录.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qz_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H48" s="4" t="str"/>
-      <x:c r="I48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">可携带奇珍配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J48" s="4" t="str"/>
-      <x:c r="K48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qizhen_carry_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="4" t="str"/>
-      <x:c r="B49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQizhenCarrySlotConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QizhenCarrySlotConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D49" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">携带位@Q奇珍录.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">carry_part</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" s="4" t="str"/>
-      <x:c r="I49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奇珍携带位配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J49" s="4" t="str"/>
-      <x:c r="K49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">qizhen_carry_slot_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="B50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbNpcConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NpcConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D50" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">npc_config@NPC配置表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">config_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NPC配置表</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">npc_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="B51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbSystemVarConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SystemVarConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D51" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ConfigSystemVar@X系统参数.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">config_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H51" s="4" t="n"/>
-      <x:c r="I51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">系统参数（含炼丹四参数）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">system_var_config</x:t>
+      <x:c r="I51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">货币配置：一行一种货币（名称、图标、说明、是否账号共享）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">currency_config</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52"/>
-      <x:c r="B52" t="str">
-        <x:v>TbAffixConfig</x:v>
-      </x:c>
-      <x:c r="C52" t="str">
-        <x:v>AffixConfig</x:v>
-      </x:c>
-      <x:c r="D52" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E52" t="str">
-        <x:v>affix_config@C词条表.xlsx</x:v>
-      </x:c>
-      <x:c r="F52" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G52" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H52"/>
-      <x:c r="I52" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">词条配置：一行一条词条，作用对象 + 修改1～修改4（每块一次修改）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J52"/>
-      <x:c r="K52" t="str">
-        <x:v>affix_config</x:v>
+      <x:c r="B52" s="2" t="inlineStr">
+        <x:is>
+          <x:t>TbCosmeticConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="2" t="inlineStr">
+        <x:is>
+          <x:t>CosmeticConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E52" s="2" t="inlineStr">
+        <x:is>
+          <x:t>cosmetic_config@H幻化配置表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="2" t="inlineStr">
+        <x:is>
+          <x:t>id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" t="inlineStr">
+        <x:is>
+          <x:t>map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I52" s="2" t="inlineStr">
+        <x:is>
+          <x:t>幻化配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K52" s="4" t="inlineStr">
+        <x:is>
+          <x:t>cosmetic_config</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53"/>
-      <x:c r="B53" t="str">
-        <x:v>TbSkillZhenyiConfig</x:v>
-      </x:c>
-      <x:c r="C53" t="str">
-        <x:v>SkillZhenyiConfig</x:v>
-      </x:c>
-      <x:c r="D53" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E53" t="str">
-        <x:v>神通真意@S神通真意表.xlsx</x:v>
-      </x:c>
-      <x:c r="F53" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G53" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H53"/>
-      <x:c r="I53" t="str">
-        <x:v>神通真意配置</x:v>
+      <x:c r="B53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbSectExchangeConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SectExchangeConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">兑换目录@Z宗门配置表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H53" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c,s</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">宗门兑换商品：开放境界、贡献价格、境界限购与周限购</x:t>
+        </x:is>
       </x:c>
       <x:c r="J53"/>
-      <x:c r="K53" t="str">
-        <x:v>skill_zhenyi_config</x:v>
+      <x:c r="K53" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sect_exchange_config</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="B54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbOwnedEntityConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OwnedEntityConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D54" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">owned_entity_config@Z从属实体表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">config_id</x:t>
+      <x:c r="A54"/>
+      <x:c r="B54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TbSectReputationLevelConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SectReputationLevelConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">声望等级@Z宗门配置表.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">level</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" t="inlineStr">
@@ -2643,267 +2594,22 @@
       </x:c>
       <x:c r="H54" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从属实体表（召唤兽/图腾/地板/火蛇；有主人、有生命周期的场上实体，将来契约宠物也在此）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">owned_entity_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="B55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbAiProfileConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AiProfileConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D55" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ai_profile@G怪物NPC行为表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物 AI 参数组（搜索间隔 / 脱战 / 回防；monster_config.ai_profile、owned_entity_config.ai_profile、npc_config.ai_profile 引用，全体法宝共用的一行由法宝全局参数 BehaviorProfile 引用）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ai_profile</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="B56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbActivityConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActivityConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D56" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">activity_config@G怪物NPC行为表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">日常活动模板（驻留 / 巡逻 / 游走 / 跟随 / 漂移 / 绕飞；spawn_config.activity、npc_config.activity、owned_entity_config.activity 引用，全体法宝共用的一行由法宝全局参数 DailyActivity 引用）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">activity_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="B57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQuestConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QuestConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D57" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">quest_config@R任务表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">任务表：一行一个任务；无标列两端都读，c 列只给客户端</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">quest_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="B58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbQuestStepConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QuestStepConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D58" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">quest_step_config@R任务表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">quest_id+step_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">list</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">任务步骤表：一行一个步骤，主键 quest_id+step_id；顺序由 next_step 决定，不是 step_id 大小</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">quest_step_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="B59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbCurrencyConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CurrencyConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D59" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ConfigAssets@X系统参数.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">config_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">货币配置：一行一种货币（名称、图标、说明、是否账号共享）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">currency_config</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="60">
-      <x:c r="B60" s="2" t="inlineStr">
-        <x:is>
-          <x:t>TbCosmeticConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C60" s="2" t="inlineStr">
-        <x:is>
-          <x:t>CosmeticConfig</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D60" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E60" s="2" t="inlineStr">
-        <x:is>
-          <x:t>cosmetic_config@H幻化配置表.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F60" s="2" t="inlineStr">
-        <x:is>
-          <x:t>id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G60" t="inlineStr">
-        <x:is>
-          <x:t>map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I60" s="2" t="inlineStr">
-        <x:is>
-          <x:t>幻化配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K60" s="4" t="inlineStr">
-        <x:is>
-          <x:t>cosmetic_config</x:t>
+          <x:t xml:space="preserve">c,s</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">宗门声望等级与待遇</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="K54" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sect_reputation_level_config</x:t>
         </x:is>
       </x:c>
     </x:row>
